--- a/resultados/angulo/erros_varredura.xlsx
+++ b/resultados/angulo/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,482 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/relatorio</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>404</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:01:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/solicitacao</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>404</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/consulta</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>404</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/regulamentacao</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>404</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/infosigilo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>404</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/legislacoes-diario/1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/equipe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:02:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/termos</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:03:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>404</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:04:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>404</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:04:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/esic/regulamentacao/relatorio</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>404</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:04:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/(44)3135 - 4000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>404</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:04:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/relatorio</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>404</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:07:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/solicitacao</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>404</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/consulta</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>404</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:08:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/regulamentacao</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:08:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/infosigilo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:08:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/angulo/erros_varredura.xlsx
+++ b/resultados/angulo/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://diario.angulo.pr.gov.br/legislacoes-diario/1</t>
+          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30 16:02:44</t>
+          <t>2026-07-30 16:04:11</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://diario.angulo.pr.gov.br/equipe</t>
+          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30 16:02:48</t>
+          <t>2026-07-30 16:04:18</t>
         </is>
       </c>
     </row>
@@ -764,23 +764,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://diario.angulo.pr.gov.br/termos</t>
+          <t>http://angulo.pr.gov.br/esic/regulamentacao/relatorio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30 16:03:21</t>
+          <t>2026-07-30 16:04:37</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=5</t>
+          <t>http://angulo.pr.gov.br/(44)3135 - 4000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30 16:04:11</t>
+          <t>2026-07-30 16:04:45</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://angulo.pr.gov.br/paginadepconteudo.php?id=4</t>
+          <t>https://www.angulo.pr.gov.br/relatorio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30 16:04:18</t>
+          <t>2026-07-30 16:07:53</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>http://angulo.pr.gov.br/esic/regulamentacao/relatorio</t>
+          <t>https://www.angulo.pr.gov.br/solicitacao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30 16:04:37</t>
+          <t>2026-07-30 16:08:01</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>http://angulo.pr.gov.br/(44)3135 - 4000</t>
+          <t>https://www.angulo.pr.gov.br/consulta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30 16:04:45</t>
+          <t>2026-07-30 16:08:08</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.angulo.pr.gov.br/relatorio</t>
+          <t>https://www.angulo.pr.gov.br/regulamentacao</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30 16:07:53</t>
+          <t>2026-07-30 16:08:15</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.angulo.pr.gov.br/solicitacao</t>
+          <t>https://www.angulo.pr.gov.br/infosigilo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30 16:08:01</t>
+          <t>2026-07-30 16:08:22</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.angulo.pr.gov.br/consulta</t>
+          <t>http://angulo.pr.gov.br/paginadepconteudo.php?id=5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -972,11 +972,11 @@
         <v>404</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30 16:08:08</t>
+          <t>2026-07-30 16:10:03</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.angulo.pr.gov.br/regulamentacao</t>
+          <t>http://angulo.pr.gov.br/paginadepconteudo.php?id=4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,11 +1000,11 @@
         <v>404</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30 16:08:15</t>
+          <t>2026-07-30 16:10:11</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.angulo.pr.gov.br/infosigilo</t>
+          <t>https://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/prefeitura?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1028,11 +1028,1439 @@
         <v>404</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30 16:08:22</t>
+          <t>2026-07-30 16:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/jogos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>404</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/futsaldeveteranos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>404</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:10:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/%C3%A2ngulo?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>404</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:10:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/sanfarmkt?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>404</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:10:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"http:/www.angulo.pr.gov.br/index.php?sessao=b054603368z5b0"</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>404</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"http:/www.produtor.adapar.pr.gov.br/comprovacaorebanho?fbclid=IwAR3h2H7dkrZD2ky3t6rnT1SsLXwNUUvlmsCeUl0rbx3RuKX-JN6dUtJx-4A"</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>404</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:11:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"https:/youtu.be/teR5DPLZrcA"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>404</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"http:/www.cohapar.pr.gov.br/modules/noticias/article.php?storyid=12948"</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>404</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/"http:/portalsaude.saude.gov.br/index.php/links-de-interesse/85-cidadao/orientacao-e-prevencao/14610-sobre-o-aedes-aegypti"</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>404</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.angulo.pr.gov.br/esic/regulamentacao/relatorio</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>404</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/prefeitura?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>404</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/jogos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>404</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/futsaldeveteranos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>404</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/%C3%A2ngulo?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>404</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/sanfarmkt?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>404</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"http:/www.angulo.pr.gov.br/index.php?sessao=b054603368z5b0"</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>404</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"http:/www.produtor.adapar.pr.gov.br/comprovacaorebanho?fbclid=IwAR3h2H7dkrZD2ky3t6rnT1SsLXwNUUvlmsCeUl0rbx3RuKX-JN6dUtJx-4A"</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>404</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:17:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"https:/youtu.be/teR5DPLZrcA"</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>404</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"http:/www.cohapar.pr.gov.br/modules/noticias/article.php?storyid=12948"</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>404</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:18:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://angulo.pr.gov.br/"http:/portalsaude.saude.gov.br/index.php/links-de-interesse/85-cidadao/orientacao-e-prevencao/14610-sobre-o-aedes-aegypti"</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>404</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:18:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/webdocview/materiadiario/2326</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>404</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/prefeitura?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>404</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/jogos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>404</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/futsaldeveteranos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>404</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/%C3%A2ngulo?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>404</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/www.facebook.com/hashtag/sanfarmkt?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>404</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"http:/www.angulo.pr.gov.br/index.php?sessao=b054603368z5b0"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>404</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"http:/www.produtor.adapar.pr.gov.br/comprovacaorebanho?fbclid=IwAR3h2H7dkrZD2ky3t6rnT1SsLXwNUUvlmsCeUl0rbx3RuKX-JN6dUtJx-4A"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>404</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"https:/youtu.be/teR5DPLZrcA"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>404</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:32:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"http:/www.cohapar.pr.gov.br/modules/noticias/article.php?storyid=12948"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>404</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:32:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>http://angulo.pr.gov.br/"http:/portalsaude.saude.gov.br/index.php/links-de-interesse/85-cidadao/orientacao-e-prevencao/14610-sobre-o-aedes-aegypti"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>404</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:32:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/(44)3135 - 4000</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>404</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:37:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/404</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>404</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:40:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/paginadepconteudo.php?id=5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>404</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:04:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/paginadepconteudo.php?id=4</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>404</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/download/materiadiario/materia/MAT-68bd6d-070420251723122326</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>404</v>
+      </c>
+      <c r="E58" t="n">
+        <v>9</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:44:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/prefeitura?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>404</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/jogos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>404</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/futsaldeveteranos?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>404</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/%C3%A2ngulo?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>404</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/www.facebook.com/hashtag/sanfarmkt?__eep__=6&amp;__cft__[0]=AZXx6J8vSI7FMYwDVZe3B40uzHvRijYduoAKxI2thwmQENpehX-2cvG7YKdN4BRDXEZ7I_S-ZmVKGL6Udtlz7LHi-xVCIXor-toiPHXH_LFloUCbFS_rhuXNdpfJKeE_uzQZWAuFUVwlo_-NwywQdTlEqcsL6f4Y9Z2PsnSM_612SsZpXe0sQFLl3lYMyeDF3mylfh9lfsUqHjyKLz-ZR1es&amp;__tn__=*NK-R"</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>404</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"http:/www.angulo.pr.gov.br/index.php?sessao=b054603368z5b0"</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>404</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"http:/www.produtor.adapar.pr.gov.br/comprovacaorebanho?fbclid=IwAR3h2H7dkrZD2ky3t6rnT1SsLXwNUUvlmsCeUl0rbx3RuKX-JN6dUtJx-4A"</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>404</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:46:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"https:/youtu.be/teR5DPLZrcA"</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>404</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"http:/www.cohapar.pr.gov.br/modules/noticias/article.php?storyid=12948"</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>404</v>
+      </c>
+      <c r="E67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:46:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>http://www.angulo.pr.gov.br/"http:/portalsaude.saude.gov.br/index.php/links-de-interesse/85-cidadao/orientacao-e-prevencao/14610-sobre-o-aedes-aegypti"</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>404</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:46:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://angulo.oxy.elotech.com.br/portaltransparencia/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: AttributeError</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/legislacoes-diario/1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>500</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/equipe</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>500</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:00:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/termos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>500</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://diario.angulo.pr.gov.br/diariooficial/materias/2887</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>500</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:00:24</t>
         </is>
       </c>
     </row>
